--- a/model_result.xlsx
+++ b/model_result.xlsx
@@ -474,7 +474,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -503,13 +503,13 @@
         <v>1.101010101010101</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02921470498499986</v>
+        <v>0.02918244421616266</v>
       </c>
       <c r="G3" t="n">
         <v>0.2095</v>
@@ -532,13 +532,13 @@
         <v>1.202020202020202</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02923265050395769</v>
+        <v>0.02919132602880471</v>
       </c>
       <c r="G4" t="n">
         <v>0.2095</v>
@@ -561,13 +561,13 @@
         <v>1.303030303030303</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02919016975276224</v>
+        <v>0.02913988256598339</v>
       </c>
       <c r="G5" t="n">
         <v>0.2095</v>
@@ -590,13 +590,13 @@
         <v>1.404040404040404</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02914673494133857</v>
+        <v>0.0291353140687861</v>
       </c>
       <c r="G6" t="n">
         <v>0.2095</v>
@@ -619,13 +619,13 @@
         <v>1.505050505050505</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02910592597553498</v>
+        <v>0.02909617386391911</v>
       </c>
       <c r="G7" t="n">
         <v>0.2095</v>
@@ -648,13 +648,13 @@
         <v>1.606060606060606</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02909537204049071</v>
+        <v>0.02913933212287078</v>
       </c>
       <c r="G8" t="n">
         <v>0.2095</v>
@@ -674,16 +674,16 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1.707070707070706</v>
+        <v>1.707070707070707</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02912989497009634</v>
+        <v>0.02917805781112669</v>
       </c>
       <c r="G9" t="n">
         <v>0.2095</v>
@@ -703,16 +703,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1.808080808080807</v>
+        <v>1.808080808080808</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02916899382817888</v>
+        <v>0.02919537644128587</v>
       </c>
       <c r="G10" t="n">
         <v>0.2095</v>
@@ -732,16 +732,16 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1.909090909090907</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02919263460690327</v>
+        <v>0.02918872388783405</v>
       </c>
       <c r="G11" t="n">
         <v>0.2095</v>
@@ -761,16 +761,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.010101010101008</v>
+        <v>2.010101010101009</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0291925084028647</v>
+        <v>0.0291888028279461</v>
       </c>
       <c r="G12" t="n">
         <v>0.2095</v>
@@ -790,16 +790,16 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.111111111111108</v>
+        <v>2.11111111111111</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02917072284278793</v>
+        <v>0.02912691538835366</v>
       </c>
       <c r="G13" t="n">
         <v>0.2095</v>
@@ -819,16 +819,16 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.212121212121209</v>
+        <v>2.212121212121211</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02914750308359113</v>
+        <v>0.0291533865794332</v>
       </c>
       <c r="G14" t="n">
         <v>0.2095</v>
@@ -848,16 +848,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2.313131313131309</v>
+        <v>2.313131313131311</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02911667151237312</v>
+        <v>0.02917478881811541</v>
       </c>
       <c r="G15" t="n">
         <v>0.2095</v>
@@ -877,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.41414141414141</v>
+        <v>2.414141414141412</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02916973661385223</v>
+        <v>0.0291920623802505</v>
       </c>
       <c r="G16" t="n">
         <v>0.2095</v>
@@ -906,16 +906,16 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2.51515151515151</v>
+        <v>2.515151515151512</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02918848174581869</v>
+        <v>0.02919877198162718</v>
       </c>
       <c r="G17" t="n">
         <v>0.2095</v>
@@ -935,16 +935,16 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2.616161616161611</v>
+        <v>2.616161616161612</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02919828251589431</v>
+        <v>0.02919153146300053</v>
       </c>
       <c r="G18" t="n">
         <v>0.2095</v>
@@ -964,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>2.717171717171712</v>
+        <v>2.717171717171713</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0291943288505052</v>
+        <v>0.02917180303590322</v>
       </c>
       <c r="G19" t="n">
         <v>0.2095</v>
@@ -993,16 +993,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2.818181818181812</v>
+        <v>2.818181818181813</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02917745046028344</v>
+        <v>0.02914713976105567</v>
       </c>
       <c r="G20" t="n">
         <v>0.2095</v>
@@ -1022,16 +1022,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>2.919191919191913</v>
+        <v>2.919191919191914</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02915327600125226</v>
+        <v>0.02913156477389386</v>
       </c>
       <c r="G21" t="n">
         <v>0.2095</v>
@@ -1051,16 +1051,16 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>3.020202020202014</v>
+        <v>3.020202020202015</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02913394592476236</v>
+        <v>0.02914919836360134</v>
       </c>
       <c r="G22" t="n">
         <v>0.2095</v>
@@ -1080,16 +1080,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>3.121212121212114</v>
+        <v>3.121212121212116</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02913816533094804</v>
+        <v>0.02911534669544593</v>
       </c>
       <c r="G23" t="n">
         <v>0.2095</v>
@@ -1109,16 +1109,16 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3.222222222222216</v>
+        <v>3.222222222222217</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02916589964121549</v>
+        <v>0.02916112639738323</v>
       </c>
       <c r="G24" t="n">
         <v>0.2095</v>
@@ -1138,16 +1138,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>3.323232323232316</v>
+        <v>3.323232323232318</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02914592744888155</v>
+        <v>0.02918977072191847</v>
       </c>
       <c r="G25" t="n">
         <v>0.2095</v>
@@ -1167,16 +1167,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>3.424242424242418</v>
+        <v>3.424242424242419</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02918306904420552</v>
+        <v>0.02919291143330502</v>
       </c>
       <c r="G26" t="n">
         <v>0.2095</v>
@@ -1196,16 +1196,16 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>3.525252525252518</v>
+        <v>3.52525252525252</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02919404217368798</v>
+        <v>0.02917382409011593</v>
       </c>
       <c r="G27" t="n">
         <v>0.2095</v>
@@ -1225,16 +1225,16 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>3.62626262626262</v>
+        <v>3.626262626262621</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02918033077546465</v>
+        <v>0.0291435319446653</v>
       </c>
       <c r="G28" t="n">
         <v>0.2095</v>
@@ -1254,16 +1254,16 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>3.72727272727272</v>
+        <v>3.727272727272722</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02915149691677681</v>
+        <v>0.02912353397953475</v>
       </c>
       <c r="G29" t="n">
         <v>0.2095</v>
@@ -1283,16 +1283,16 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>3.828282828282822</v>
+        <v>3.828282828282823</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0291262954392668</v>
+        <v>0.02907907555839143</v>
       </c>
       <c r="G30" t="n">
         <v>0.2095</v>
@@ -1312,16 +1312,16 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>3.929292929292922</v>
+        <v>3.929292929292924</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.02913224655175794</v>
+        <v>0.02917790379303895</v>
       </c>
       <c r="G31" t="n">
         <v>0.2095</v>
@@ -1341,16 +1341,16 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>4.030303030303024</v>
+        <v>4.030303030303025</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.02910565946623361</v>
+        <v>0.02919957708057087</v>
       </c>
       <c r="G32" t="n">
         <v>0.2095</v>
@@ -1373,13 +1373,13 @@
         <v>4.131313131313123</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.02921102007433635</v>
+        <v>0.02919359161908715</v>
       </c>
       <c r="G33" t="n">
         <v>0.2095</v>
@@ -1399,16 +1399,16 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>4.232323232323225</v>
+        <v>4.232323232323223</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.02919857373475386</v>
+        <v>0.02917872412891291</v>
       </c>
       <c r="G34" t="n">
         <v>0.2095</v>
@@ -1428,16 +1428,16 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>4.333333333333324</v>
+        <v>4.333333333333322</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02918248962543291</v>
+        <v>0.02915558777091826</v>
       </c>
       <c r="G35" t="n">
         <v>0.2095</v>
@@ -1460,13 +1460,13 @@
         <v>4.434343434343424</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.02916146194410028</v>
+        <v>0.02913598474307646</v>
       </c>
       <c r="G36" t="n">
         <v>0.2095</v>
@@ -1486,16 +1486,16 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>4.535353535353524</v>
+        <v>4.535353535353522</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.02913998232619983</v>
+        <v>0.02913713064882007</v>
       </c>
       <c r="G37" t="n">
         <v>0.2095</v>
@@ -1515,16 +1515,16 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>4.636363636363624</v>
+        <v>4.636363636363622</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.02913411564681248</v>
+        <v>0.02916595657226265</v>
       </c>
       <c r="G38" t="n">
         <v>0.2095</v>
@@ -1544,16 +1544,16 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>4.737373737373725</v>
+        <v>4.737373737373724</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.02915762920665982</v>
+        <v>0.02919999111982917</v>
       </c>
       <c r="G39" t="n">
         <v>0.2095</v>
@@ -1573,16 +1573,16 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>4.838383838383825</v>
+        <v>4.838383838383824</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.02919232890672313</v>
+        <v>0.02919202922779534</v>
       </c>
       <c r="G40" t="n">
         <v>0.2095</v>
@@ -1602,16 +1602,16 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>4.939393939393925</v>
+        <v>4.939393939393924</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.02921801939736709</v>
+        <v>0.02918885764968536</v>
       </c>
       <c r="G41" t="n">
         <v>0.2095</v>
@@ -1634,13 +1634,13 @@
         <v>5.040404040404026</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.02918947122671119</v>
+        <v>0.02918249537043332</v>
       </c>
       <c r="G42" t="n">
         <v>0.2095</v>
@@ -1663,13 +1663,13 @@
         <v>5.141414141414126</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02918383495513202</v>
+        <v>0.02915499219503732</v>
       </c>
       <c r="G43" t="n">
         <v>0.2095</v>
@@ -1692,13 +1692,13 @@
         <v>5.242424242424227</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0291629444135935</v>
+        <v>0.02912857283806162</v>
       </c>
       <c r="G44" t="n">
         <v>0.2095</v>
@@ -1721,13 +1721,13 @@
         <v>5.343434343434328</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.02913403300087583</v>
+        <v>0.02912991580253977</v>
       </c>
       <c r="G45" t="n">
         <v>0.2095</v>
@@ -1750,13 +1750,13 @@
         <v>5.44444444444443</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.02912541462756524</v>
+        <v>0.02915501008284166</v>
       </c>
       <c r="G46" t="n">
         <v>0.2095</v>
@@ -1779,13 +1779,13 @@
         <v>5.54545454545453</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.02914821458629658</v>
+        <v>0.02917811576099155</v>
       </c>
       <c r="G47" t="n">
         <v>0.2095</v>
@@ -1808,13 +1808,13 @@
         <v>5.646464646464631</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02917276136288815</v>
+        <v>0.0291890205872191</v>
       </c>
       <c r="G48" t="n">
         <v>0.2095</v>
@@ -1837,13 +1837,13 @@
         <v>5.747474747474732</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.02918731742696209</v>
+        <v>0.02920378248522909</v>
       </c>
       <c r="G49" t="n">
         <v>0.2095</v>
@@ -1866,13 +1866,13 @@
         <v>5.848484848484834</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.02918633459561317</v>
+        <v>0.02920458071906912</v>
       </c>
       <c r="G50" t="n">
         <v>0.2095</v>
@@ -1895,13 +1895,13 @@
         <v>5.949494949494935</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.02919378900650841</v>
+        <v>0.029140743983317</v>
       </c>
       <c r="G51" t="n">
         <v>0.2095</v>
@@ -1924,13 +1924,13 @@
         <v>6.050505050505035</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.02916695503777665</v>
+        <v>0.029135932773338</v>
       </c>
       <c r="G52" t="n">
         <v>0.2095</v>
@@ -1953,13 +1953,13 @@
         <v>6.151515151515136</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.02913186015645971</v>
+        <v>0.02915650411044909</v>
       </c>
       <c r="G53" t="n">
         <v>0.2095</v>
@@ -1982,13 +1982,13 @@
         <v>6.252525252525237</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.02915095405284869</v>
+        <v>0.02919121412043122</v>
       </c>
       <c r="G54" t="n">
         <v>0.2095</v>
@@ -2011,13 +2011,13 @@
         <v>6.353535353535339</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.02918302501493212</v>
+        <v>0.02921813367945622</v>
       </c>
       <c r="G55" t="n">
         <v>0.2095</v>
@@ -2040,13 +2040,13 @@
         <v>6.454545454545439</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.02921348936601636</v>
+        <v>0.02922517171009537</v>
       </c>
       <c r="G56" t="n">
         <v>0.2095</v>
@@ -2069,13 +2069,13 @@
         <v>6.55555555555554</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.02922628394970841</v>
+        <v>0.02920812328941173</v>
       </c>
       <c r="G57" t="n">
         <v>0.2095</v>
@@ -2098,13 +2098,13 @@
         <v>6.656565656565641</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.02921533595908272</v>
+        <v>0.02915637291843828</v>
       </c>
       <c r="G58" t="n">
         <v>0.2095</v>
@@ -2127,13 +2127,13 @@
         <v>6.757575757575743</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.02918280127987055</v>
+        <v>0.02913694959625329</v>
       </c>
       <c r="G59" t="n">
         <v>0.2095</v>
@@ -2156,13 +2156,13 @@
         <v>6.858585858585843</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.02914353765507046</v>
+        <v>0.02912454833451775</v>
       </c>
       <c r="G60" t="n">
         <v>0.2095</v>
@@ -2185,13 +2185,13 @@
         <v>6.959595959595944</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.02912712196745423</v>
+        <v>0.02914610578870987</v>
       </c>
       <c r="G61" t="n">
         <v>0.2095</v>
@@ -2214,13 +2214,13 @@
         <v>7.060606060606045</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.02913923804407962</v>
+        <v>0.02917001933447534</v>
       </c>
       <c r="G62" t="n">
         <v>0.2095</v>
@@ -2243,13 +2243,13 @@
         <v>7.161616161616147</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.02916444115299342</v>
+        <v>0.02918537221049634</v>
       </c>
       <c r="G63" t="n">
         <v>0.2095</v>
@@ -2272,13 +2272,13 @@
         <v>7.262626262626247</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.02918232975410672</v>
+        <v>0.02918609809588574</v>
       </c>
       <c r="G64" t="n">
         <v>0.2095</v>
@@ -2301,13 +2301,13 @@
         <v>7.363636363636348</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.02918696866429867</v>
+        <v>0.02917254787804205</v>
       </c>
       <c r="G65" t="n">
         <v>0.2095</v>
@@ -2330,13 +2330,13 @@
         <v>7.464646464646449</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.02917685268713011</v>
+        <v>0.02915179026391222</v>
       </c>
       <c r="G66" t="n">
         <v>0.2095</v>
@@ -2359,13 +2359,13 @@
         <v>7.565656565656551</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.02915721175111164</v>
+        <v>0.02912549471439977</v>
       </c>
       <c r="G67" t="n">
         <v>0.2095</v>
@@ -2388,13 +2388,13 @@
         <v>7.666666666666652</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.02914031802972544</v>
+        <v>0.02907983181090464</v>
       </c>
       <c r="G68" t="n">
         <v>0.2095</v>
@@ -2417,13 +2417,13 @@
         <v>7.767676767676752</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.02910876403478868</v>
+        <v>0.02917813464012684</v>
       </c>
       <c r="G69" t="n">
         <v>0.2095</v>
@@ -2446,13 +2446,13 @@
         <v>7.868686868686853</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0290866139448202</v>
+        <v>0.02921384519354246</v>
       </c>
       <c r="G70" t="n">
         <v>0.2095</v>
@@ -2475,13 +2475,13 @@
         <v>7.969696969696955</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0292051954853341</v>
+        <v>0.02922809021219043</v>
       </c>
       <c r="G71" t="n">
         <v>0.2095</v>
@@ -2504,13 +2504,13 @@
         <v>8.070707070707053</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.02922725647785715</v>
+        <v>0.02921939103871278</v>
       </c>
       <c r="G72" t="n">
         <v>0.2095</v>
@@ -2533,13 +2533,13 @@
         <v>8.171717171717152</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.02922469731843685</v>
+        <v>0.02918864962210599</v>
       </c>
       <c r="G73" t="n">
         <v>0.2095</v>
@@ -2559,16 +2559,16 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>8.27272727272725</v>
+        <v>8.272727272727252</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0291987523602517</v>
+        <v>0.02914540237560007</v>
       </c>
       <c r="G74" t="n">
         <v>0.2095</v>
@@ -2588,16 +2588,16 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>8.373737373737349</v>
+        <v>8.373737373737351</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.02915717856480855</v>
+        <v>0.02910824823604515</v>
       </c>
       <c r="G75" t="n">
         <v>0.2095</v>
@@ -2617,16 +2617,16 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>8.474747474747447</v>
+        <v>8.474747474747449</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.02911584866702079</v>
+        <v>0.02916236651008956</v>
       </c>
       <c r="G76" t="n">
         <v>0.2095</v>
@@ -2649,13 +2649,13 @@
         <v>8.575757575757546</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.02909992877993702</v>
+        <v>0.02916477055120659</v>
       </c>
       <c r="G77" t="n">
         <v>0.2095</v>
@@ -2675,16 +2675,16 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>8.676767676767646</v>
+        <v>8.676767676767648</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.02913374526510669</v>
+        <v>0.02917962243847138</v>
       </c>
       <c r="G78" t="n">
         <v>0.2095</v>
@@ -2704,16 +2704,16 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>8.777777777777745</v>
+        <v>8.777777777777747</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.02920514768637344</v>
+        <v>0.0291859919497974</v>
       </c>
       <c r="G79" t="n">
         <v>0.2095</v>
@@ -2733,16 +2733,16 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>8.878787878787843</v>
+        <v>8.878787878787845</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.02918688533091155</v>
+        <v>0.02917759972085495</v>
       </c>
       <c r="G80" t="n">
         <v>0.2095</v>
@@ -2762,16 +2762,16 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>8.979797979797942</v>
+        <v>8.979797979797944</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.02917967815303627</v>
+        <v>0.02915947076523272</v>
       </c>
       <c r="G81" t="n">
         <v>0.2095</v>
@@ -2791,16 +2791,16 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>9.080808080808042</v>
+        <v>9.080808080808044</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.02916374059135771</v>
+        <v>0.02914248411371016</v>
       </c>
       <c r="G82" t="n">
         <v>0.2095</v>
@@ -2820,16 +2820,16 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>9.181818181818143</v>
+        <v>9.181818181818144</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.02914577392926207</v>
+        <v>0.02914455100788548</v>
       </c>
       <c r="G83" t="n">
         <v>0.2095</v>
@@ -2849,16 +2849,16 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>9.282828282828243</v>
+        <v>9.282828282828245</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.02914229597397877</v>
+        <v>0.02916561875355872</v>
       </c>
       <c r="G84" t="n">
         <v>0.2095</v>
@@ -2878,16 +2878,16 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>9.383838383838345</v>
+        <v>9.383838383838347</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.02916082709694329</v>
+        <v>0.02915520429736511</v>
       </c>
       <c r="G85" t="n">
         <v>0.2095</v>
@@ -2907,16 +2907,16 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>9.484848484848445</v>
+        <v>9.484848484848447</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.02918329154285087</v>
+        <v>0.02918519264296025</v>
       </c>
       <c r="G86" t="n">
         <v>0.2095</v>
@@ -2936,16 +2936,16 @@
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>9.585858585858547</v>
+        <v>9.585858585858549</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.02917483694028307</v>
+        <v>0.02923015216517481</v>
       </c>
       <c r="G87" t="n">
         <v>0.2095</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>9.686868686868648</v>
+        <v>9.68686868686865</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.02921326845956805</v>
+        <v>0.02920339158385523</v>
       </c>
       <c r="G88" t="n">
         <v>0.2095</v>
@@ -2994,16 +2994,16 @@
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>9.787878787878748</v>
+        <v>9.78787878787875</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.02921513668821458</v>
+        <v>0.02916315941631676</v>
       </c>
       <c r="G89" t="n">
         <v>0.2095</v>
@@ -3023,16 +3023,16 @@
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>9.88888888888885</v>
+        <v>9.888888888888852</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.02917324862801936</v>
+        <v>0.02911979933269365</v>
       </c>
       <c r="G90" t="n">
         <v>0.2095</v>
@@ -3052,16 +3052,16 @@
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>9.989898989898951</v>
+        <v>9.989898989898952</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.02912902546966498</v>
+        <v>0.02909771722104632</v>
       </c>
       <c r="G91" t="n">
         <v>0.2095</v>
@@ -3084,13 +3084,13 @@
         <v>10.09090909090905</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.02909875249424949</v>
+        <v>0.02912210631191598</v>
       </c>
       <c r="G92" t="n">
         <v>0.2095</v>
@@ -3113,13 +3113,13 @@
         <v>10.19191919191915</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.02911168998947423</v>
+        <v>0.02916188262287044</v>
       </c>
       <c r="G93" t="n">
         <v>0.2095</v>
@@ -3139,16 +3139,16 @@
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>10.29292929292925</v>
+        <v>10.29292929292926</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.02915143616581848</v>
+        <v>0.02922091874626024</v>
       </c>
       <c r="G94" t="n">
         <v>0.2095</v>
@@ -3171,13 +3171,13 @@
         <v>10.39393939393936</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.02918447444019337</v>
+        <v>0.02920262307170044</v>
       </c>
       <c r="G95" t="n">
         <v>0.2095</v>
@@ -3200,13 +3200,13 @@
         <v>10.49494949494946</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.02923460161109327</v>
+        <v>0.02916547234814856</v>
       </c>
       <c r="G96" t="n">
         <v>0.2095</v>
@@ -3229,13 +3229,13 @@
         <v>10.59595959595956</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.02918395593471963</v>
+        <v>0.0291479905083844</v>
       </c>
       <c r="G97" t="n">
         <v>0.2095</v>
@@ -3258,13 +3258,13 @@
         <v>10.69696969696966</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.02915138660112756</v>
+        <v>0.02914295128061275</v>
       </c>
       <c r="G98" t="n">
         <v>0.2095</v>
@@ -3287,13 +3287,13 @@
         <v>10.79797979797976</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.02914304395407074</v>
+        <v>0.0291596957817408</v>
       </c>
       <c r="G99" t="n">
         <v>0.2095</v>
@@ -3316,13 +3316,13 @@
         <v>10.89898989898986</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.02915554582321393</v>
+        <v>0.02918140913448477</v>
       </c>
       <c r="G100" t="n">
         <v>0.2095</v>
@@ -3345,13 +3345,13 @@
         <v>10.99999999999996</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.02915828856670252</v>
+        <v>0.02916368452664037</v>
       </c>
       <c r="G101" t="n">
         <v>0.2095</v>
@@ -3374,13 +3374,13 @@
         <v>11.99999999999996</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0.02915828856670252</v>
+        <v>0.02916368452664037</v>
       </c>
       <c r="G102" t="n">
         <v>0.2095</v>
@@ -3403,13 +3403,13 @@
         <v>12.10101010101006</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>0.02917119812588745</v>
+        <v>0.02917182364284595</v>
       </c>
       <c r="G103" t="n">
         <v>0.2095</v>
@@ -3429,16 +3429,16 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>12.20202020202016</v>
+        <v>12.20202020202017</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0.02916927666650223</v>
+        <v>0.02917061129620289</v>
       </c>
       <c r="G104" t="n">
         <v>0.2095</v>
@@ -3458,16 +3458,16 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>12.30303030303026</v>
+        <v>12.30303030303027</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0.02919015079583598</v>
+        <v>0.02919138717117781</v>
       </c>
       <c r="G105" t="n">
         <v>0.2095</v>
@@ -3490,13 +3490,13 @@
         <v>12.40404040404037</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0.02918273433530438</v>
+        <v>0.02918937185518306</v>
       </c>
       <c r="G106" t="n">
         <v>0.2095</v>
@@ -3519,13 +3519,13 @@
         <v>12.50505050505047</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0.02914823195013057</v>
+        <v>0.02915221644738732</v>
       </c>
       <c r="G107" t="n">
         <v>0.2095</v>
@@ -3548,13 +3548,13 @@
         <v>12.60606060606057</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>0.02918066438993335</v>
+        <v>0.02915827835389952</v>
       </c>
       <c r="G108" t="n">
         <v>0.2095</v>
@@ -3577,13 +3577,13 @@
         <v>12.70707070707067</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0.02918836455737593</v>
+        <v>0.02919319338676946</v>
       </c>
       <c r="G109" t="n">
         <v>0.2095</v>
@@ -3606,13 +3606,13 @@
         <v>12.80808080808077</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>0.02913488122137243</v>
+        <v>0.02914512243827495</v>
       </c>
       <c r="G110" t="n">
         <v>0.2095</v>
@@ -3635,13 +3635,13 @@
         <v>12.90909090909087</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>0.02920270639881815</v>
+        <v>0.02918079852234244</v>
       </c>
       <c r="G111" t="n">
         <v>0.2095</v>
@@ -3664,13 +3664,13 @@
         <v>13.01010101010097</v>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0.02917321156058857</v>
+        <v>0.02918168500538048</v>
       </c>
       <c r="G112" t="n">
         <v>0.2095</v>
@@ -3693,13 +3693,13 @@
         <v>13.11111111111107</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0.02913033566580732</v>
+        <v>0.02913819136094659</v>
       </c>
       <c r="G113" t="n">
         <v>0.2095</v>
@@ -3719,16 +3719,16 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>13.21212121212117</v>
+        <v>13.21212121212118</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>0.02923027283354361</v>
+        <v>0.0292195655753517</v>
       </c>
       <c r="G114" t="n">
         <v>0.2095</v>
@@ -3748,16 +3748,16 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>13.31313131313127</v>
+        <v>13.31313131313128</v>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>0.02913412391914236</v>
+        <v>0.0291625648305105</v>
       </c>
       <c r="G115" t="n">
         <v>0.2095</v>
@@ -3777,16 +3777,16 @@
         <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>13.41414141414137</v>
+        <v>13.41414141414138</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0291461373031244</v>
+        <v>0.02912474625550452</v>
       </c>
       <c r="G116" t="n">
         <v>0.2095</v>
@@ -3809,13 +3809,13 @@
         <v>13.51515151515148</v>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>0.02920836332370316</v>
+        <v>0.02919653031978807</v>
       </c>
       <c r="G117" t="n">
         <v>0.2095</v>
@@ -3838,13 +3838,13 @@
         <v>13.61616161616158</v>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>0.02909654893938982</v>
+        <v>0.02912676118777997</v>
       </c>
       <c r="G118" t="n">
         <v>0.2095</v>
@@ -3867,13 +3867,13 @@
         <v>13.71717171717168</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0.02918592404564837</v>
+        <v>0.02918052791076117</v>
       </c>
       <c r="G119" t="n">
         <v>0.2095</v>
@@ -3896,13 +3896,13 @@
         <v>13.81818181818178</v>
       </c>
       <c r="D120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0.02914845060171512</v>
+        <v>0.02916435392033176</v>
       </c>
       <c r="G120" t="n">
         <v>0.2095</v>
@@ -3925,13 +3925,13 @@
         <v>13.91919191919188</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>0.02916300722786625</v>
+        <v>0.0291595180796159</v>
       </c>
       <c r="G121" t="n">
         <v>0.2095</v>
@@ -3954,13 +3954,13 @@
         <v>14.02020202020198</v>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>0.02918109581250165</v>
+        <v>0.02919860997876468</v>
       </c>
       <c r="G122" t="n">
         <v>0.2095</v>
@@ -3983,13 +3983,13 @@
         <v>14.12121212121208</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>0.02914184707433662</v>
+        <v>0.02913509773713845</v>
       </c>
       <c r="G123" t="n">
         <v>0.2095</v>
@@ -4012,13 +4012,13 @@
         <v>14.22222222222218</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>0.02920083826578511</v>
+        <v>0.02919666135112415</v>
       </c>
       <c r="G124" t="n">
         <v>0.2095</v>
@@ -4038,16 +4038,16 @@
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>14.32323232323228</v>
+        <v>14.32323232323229</v>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>0.02915472979290061</v>
+        <v>0.02919882260338471</v>
       </c>
       <c r="G125" t="n">
         <v>0.2095</v>
@@ -4067,16 +4067,16 @@
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>14.42424242424238</v>
+        <v>14.42424242424239</v>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0.02916430060643222</v>
+        <v>0.0291005726108616</v>
       </c>
       <c r="G126" t="n">
         <v>0.2095</v>
@@ -4099,13 +4099,13 @@
         <v>14.52525252525249</v>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0.02922257959900567</v>
+        <v>0.02922026893900536</v>
       </c>
       <c r="G127" t="n">
         <v>0.2095</v>
@@ -4128,13 +4128,13 @@
         <v>14.62626262626259</v>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>0.02911388877431748</v>
+        <v>0.02916156866969673</v>
       </c>
       <c r="G128" t="n">
         <v>0.2095</v>
@@ -4157,13 +4157,13 @@
         <v>14.72727272727269</v>
       </c>
       <c r="D129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02918280827785351</v>
+        <v>0.02911579889187817</v>
       </c>
       <c r="G129" t="n">
         <v>0.2095</v>
@@ -4186,13 +4186,13 @@
         <v>14.82828282828279</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0.02920556369624762</v>
+        <v>0.02920184549247691</v>
       </c>
       <c r="G130" t="n">
         <v>0.2095</v>
@@ -4215,13 +4215,13 @@
         <v>14.92929292929289</v>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0.02908331335570497</v>
+        <v>0.02911209070052659</v>
       </c>
       <c r="G131" t="n">
         <v>0.2095</v>
@@ -4244,13 +4244,13 @@
         <v>15.03030303030299</v>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>0.02919633725049349</v>
+        <v>0.02917990669935399</v>
       </c>
       <c r="G132" t="n">
         <v>0.2095</v>
@@ -4273,13 +4273,13 @@
         <v>15.13131313131309</v>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>0.02913692556097714</v>
+        <v>0.02915621772413157</v>
       </c>
       <c r="G133" t="n">
         <v>0.2095</v>
@@ -4302,13 +4302,13 @@
         <v>15.23232323232319</v>
       </c>
       <c r="D134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.02916083191711156</v>
+        <v>0.02916495729137745</v>
       </c>
       <c r="G134" t="n">
         <v>0.2095</v>
@@ -4328,16 +4328,16 @@
         <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>15.33333333333329</v>
+        <v>15.3333333333333</v>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>0.02917477726045049</v>
+        <v>0.02918705219874856</v>
       </c>
       <c r="G135" t="n">
         <v>0.2095</v>
@@ -4360,13 +4360,13 @@
         <v>15.4343434343434</v>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>0.02914704576293212</v>
+        <v>0.02913803673464378</v>
       </c>
       <c r="G136" t="n">
         <v>0.2095</v>
@@ -4389,13 +4389,13 @@
         <v>15.5353535353535</v>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>0.02919389842885968</v>
+        <v>0.02920575943080917</v>
       </c>
       <c r="G137" t="n">
         <v>0.2095</v>
@@ -4418,13 +4418,13 @@
         <v>15.6363636363636</v>
       </c>
       <c r="D138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>0.02914559308483896</v>
+        <v>0.02917191501381413</v>
       </c>
       <c r="G138" t="n">
         <v>0.2095</v>
@@ -4447,13 +4447,13 @@
         <v>15.7373737373737</v>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>0.02918682949862781</v>
+        <v>0.02913002675644427</v>
       </c>
       <c r="G139" t="n">
         <v>0.2095</v>
@@ -4476,13 +4476,13 @@
         <v>15.8383838383838</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>0.02919986530318925</v>
+        <v>0.02923686993471445</v>
       </c>
       <c r="G140" t="n">
         <v>0.2095</v>
@@ -4505,13 +4505,13 @@
         <v>15.9393939393939</v>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>0.02911330845558157</v>
+        <v>0.02913443867742087</v>
       </c>
       <c r="G141" t="n">
         <v>0.2095</v>
@@ -4531,16 +4531,16 @@
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>16.040404040404</v>
+        <v>16.04040404040401</v>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>0.02921887138732869</v>
+        <v>0.02913738296863195</v>
       </c>
       <c r="G142" t="n">
         <v>0.2095</v>
@@ -4560,16 +4560,16 @@
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>16.1414141414141</v>
+        <v>16.14141414141411</v>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>0.02918516214764988</v>
+        <v>0.02921203308243104</v>
       </c>
       <c r="G143" t="n">
         <v>0.2095</v>
@@ -4589,16 +4589,16 @@
         <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>16.2424242424242</v>
+        <v>16.24242424242421</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>0.02908905247232446</v>
+        <v>0.02909222665004245</v>
       </c>
       <c r="G144" t="n">
         <v>0.2095</v>
@@ -4621,13 +4621,13 @@
         <v>16.3434343434343</v>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>0.02921576319457658</v>
+        <v>0.02918178197347678</v>
       </c>
       <c r="G145" t="n">
         <v>0.2095</v>
@@ -4650,13 +4650,13 @@
         <v>16.44444444444441</v>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>0.02912032718084346</v>
+        <v>0.02914793036550409</v>
       </c>
       <c r="G146" t="n">
         <v>0.2095</v>
@@ -4676,16 +4676,16 @@
         <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>16.5454545454545</v>
+        <v>16.54545454545451</v>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>0.02915812960583365</v>
+        <v>0.02916416964946051</v>
       </c>
       <c r="G147" t="n">
         <v>0.2095</v>
@@ -4708,13 +4708,13 @@
         <v>16.64646464646461</v>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>0.02917063088430781</v>
+        <v>0.02917837165724177</v>
       </c>
       <c r="G148" t="n">
         <v>0.2095</v>
@@ -4737,13 +4737,13 @@
         <v>16.74747474747471</v>
       </c>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>0.02914561715931146</v>
+        <v>0.02914664209194221</v>
       </c>
       <c r="G149" t="n">
         <v>0.2095</v>
@@ -4766,13 +4766,13 @@
         <v>16.84848484848481</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>0.02918726908904689</v>
+        <v>0.02920086106940428</v>
       </c>
       <c r="G150" t="n">
         <v>0.2095</v>
@@ -4795,13 +4795,13 @@
         <v>16.94949494949491</v>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>0.02914281924278472</v>
+        <v>0.02915344207344559</v>
       </c>
       <c r="G151" t="n">
         <v>0.2095</v>
@@ -4824,13 +4824,13 @@
         <v>17.05050505050501</v>
       </c>
       <c r="D152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.02919304915263295</v>
+        <v>0.02916828271624427</v>
       </c>
       <c r="G152" t="n">
         <v>0.2095</v>
@@ -4853,13 +4853,13 @@
         <v>17.15151515151511</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0.02917704838561839</v>
+        <v>0.02922721486129634</v>
       </c>
       <c r="G153" t="n">
         <v>0.2095</v>
@@ -4882,13 +4882,13 @@
         <v>17.25252525252521</v>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>0.02913616725425176</v>
+        <v>0.02911163685316093</v>
       </c>
       <c r="G154" t="n">
         <v>0.2095</v>
@@ -4911,13 +4911,13 @@
         <v>17.35353535353531</v>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0292319854046793</v>
+        <v>0.02916042207109014</v>
       </c>
       <c r="G155" t="n">
         <v>0.2095</v>
@@ -4940,13 +4940,13 @@
         <v>17.45454545454541</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0.02915283988255393</v>
+        <v>0.02917470257363723</v>
       </c>
       <c r="G156" t="n">
         <v>0.2095</v>
@@ -4969,13 +4969,13 @@
         <v>17.55555555555551</v>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0.02911971204845339</v>
+        <v>0.02913759840188428</v>
       </c>
       <c r="G157" t="n">
         <v>0.2095</v>
@@ -4995,16 +4995,16 @@
         <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>17.65656565656561</v>
+        <v>17.65656565656562</v>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0.02919087140144503</v>
+        <v>0.02918551839009507</v>
       </c>
       <c r="G158" t="n">
         <v>0.2095</v>
@@ -5027,13 +5027,13 @@
         <v>17.75757575757572</v>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>0.02912354017550122</v>
+        <v>0.02914321818195049</v>
       </c>
       <c r="G159" t="n">
         <v>0.2095</v>
@@ -5056,13 +5056,13 @@
         <v>17.85858585858582</v>
       </c>
       <c r="D160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0.02918110788721486</v>
+        <v>0.02918976732020145</v>
       </c>
       <c r="G160" t="n">
         <v>0.2095</v>
@@ -5085,13 +5085,13 @@
         <v>17.95959595959592</v>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>0.02915529260029073</v>
+        <v>0.0291732274727917</v>
       </c>
       <c r="G161" t="n">
         <v>0.2095</v>
@@ -5114,13 +5114,13 @@
         <v>18.06060606060602</v>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0291745683511201</v>
+        <v>0.02914582399512107</v>
       </c>
       <c r="G162" t="n">
         <v>0.2095</v>
@@ -5143,13 +5143,13 @@
         <v>18.16161616161612</v>
       </c>
       <c r="D163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>0.02918867260128831</v>
+        <v>0.02922772153797987</v>
       </c>
       <c r="G163" t="n">
         <v>0.2095</v>
@@ -5172,13 +5172,13 @@
         <v>18.26262626262622</v>
       </c>
       <c r="D164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>0.02913617068752308</v>
+        <v>0.02914781908953494</v>
       </c>
       <c r="G164" t="n">
         <v>0.2095</v>
@@ -5201,13 +5201,13 @@
         <v>18.36363636363632</v>
       </c>
       <c r="D165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0.02921632085459392</v>
+        <v>0.02913104138854118</v>
       </c>
       <c r="G165" t="n">
         <v>0.2095</v>
@@ -5230,13 +5230,13 @@
         <v>18.46464646464642</v>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>0.02918688452144834</v>
+        <v>0.02919178994269407</v>
       </c>
       <c r="G166" t="n">
         <v>0.2095</v>
@@ -5259,13 +5259,13 @@
         <v>18.56565656565652</v>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>0.02909819103228242</v>
+        <v>0.02912407154133222</v>
       </c>
       <c r="G167" t="n">
         <v>0.2095</v>
@@ -5288,13 +5288,13 @@
         <v>18.66666666666663</v>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>0.02919180464105324</v>
+        <v>0.02918354625107098</v>
       </c>
       <c r="G168" t="n">
         <v>0.2095</v>
@@ -5317,13 +5317,13 @@
         <v>18.76767676767673</v>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>0.02913830953779493</v>
+        <v>0.02915536082257017</v>
       </c>
       <c r="G169" t="n">
         <v>0.2095</v>
@@ -5346,13 +5346,13 @@
         <v>18.86868686868683</v>
       </c>
       <c r="D170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>0.02916873451967799</v>
+        <v>0.02917260923399751</v>
       </c>
       <c r="G170" t="n">
         <v>0.2095</v>
@@ -5375,13 +5375,13 @@
         <v>18.96969696969693</v>
       </c>
       <c r="D171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>0.02917198854376221</v>
+        <v>0.02919140902468533</v>
       </c>
       <c r="G171" t="n">
         <v>0.2095</v>
@@ -5404,13 +5404,13 @@
         <v>19.07070707070703</v>
       </c>
       <c r="D172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>0.02915429132794086</v>
+        <v>0.0291332885097964</v>
       </c>
       <c r="G172" t="n">
         <v>0.2095</v>
@@ -5433,13 +5433,13 @@
         <v>19.17171717171713</v>
       </c>
       <c r="D173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>0.02919840286256721</v>
+        <v>0.0292126869886739</v>
       </c>
       <c r="G173" t="n">
         <v>0.2095</v>
@@ -5462,13 +5462,13 @@
         <v>19.27272727272723</v>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>0.0291452759097488</v>
+        <v>0.0291866301939247</v>
       </c>
       <c r="G174" t="n">
         <v>0.2095</v>
@@ -5491,13 +5491,13 @@
         <v>19.37373737373733</v>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>0.02918611752872815</v>
+        <v>0.02910083312307782</v>
       </c>
       <c r="G175" t="n">
         <v>0.2095</v>
@@ -5520,13 +5520,13 @@
         <v>19.47474747474743</v>
       </c>
       <c r="D176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>0.02921710193152888</v>
+        <v>0.0291934578960764</v>
       </c>
       <c r="G176" t="n">
         <v>0.2095</v>
@@ -5549,13 +5549,13 @@
         <v>19.57575757575753</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>0.02910160869293265</v>
+        <v>0.02913761373415124</v>
       </c>
       <c r="G177" t="n">
         <v>0.2095</v>
@@ -5578,13 +5578,13 @@
         <v>19.67676767676763</v>
       </c>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>0.02917455587173766</v>
+        <v>0.02916924777833486</v>
       </c>
       <c r="G178" t="n">
         <v>0.2095</v>
@@ -5607,13 +5607,13 @@
         <v>19.77777777777774</v>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>0.0291644535925402</v>
+        <v>0.02917280570481745</v>
       </c>
       <c r="G179" t="n">
         <v>0.2095</v>
@@ -5636,13 +5636,13 @@
         <v>19.87878787878784</v>
       </c>
       <c r="D180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>0.02914711293482622</v>
+        <v>0.02915215632450887</v>
       </c>
       <c r="G180" t="n">
         <v>0.2095</v>
@@ -5665,13 +5665,13 @@
         <v>19.97979797979794</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0.02918424387636821</v>
+        <v>0.02919897078766242</v>
       </c>
       <c r="G181" t="n">
         <v>0.2095</v>
@@ -5694,13 +5694,13 @@
         <v>20.08080808080804</v>
       </c>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>0.02914170386956971</v>
+        <v>0.02914492558183094</v>
       </c>
       <c r="G182" t="n">
         <v>0.2095</v>
@@ -5723,13 +5723,13 @@
         <v>20.18181818181814</v>
       </c>
       <c r="D183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>0.02919444805676684</v>
+        <v>0.02918442542674599</v>
       </c>
       <c r="G183" t="n">
         <v>0.2095</v>
@@ -5752,13 +5752,13 @@
         <v>20.28282828282824</v>
       </c>
       <c r="D184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>0.02916574571561415</v>
+        <v>0.02921442405148658</v>
       </c>
       <c r="G184" t="n">
         <v>0.2095</v>
@@ -5781,13 +5781,13 @@
         <v>20.38383838383834</v>
       </c>
       <c r="D185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>0.02915426114568796</v>
+        <v>0.02910292874008159</v>
       </c>
       <c r="G185" t="n">
         <v>0.2095</v>
@@ -5810,13 +5810,13 @@
         <v>20.48484848484844</v>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>0.02922790963759542</v>
+        <v>0.02917792443643927</v>
       </c>
       <c r="G186" t="n">
         <v>0.2095</v>
@@ -5839,13 +5839,13 @@
         <v>20.58585858585855</v>
       </c>
       <c r="D187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>0.02913279902329233</v>
+        <v>0.0291637194815251</v>
       </c>
       <c r="G187" t="n">
         <v>0.2095</v>
@@ -5868,13 +5868,13 @@
         <v>20.68686868686864</v>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>0.02914503950803731</v>
+        <v>0.02914753939019567</v>
       </c>
       <c r="G188" t="n">
         <v>0.2095</v>
@@ -5897,13 +5897,13 @@
         <v>20.78787878787875</v>
       </c>
       <c r="D189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>0.02918667569106618</v>
+        <v>0.02918558674175265</v>
       </c>
       <c r="G189" t="n">
         <v>0.2095</v>
@@ -5926,13 +5926,13 @@
         <v>20.88888888888885</v>
       </c>
       <c r="D190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>0.02912645590655782</v>
+        <v>0.02913985487226303</v>
       </c>
       <c r="G190" t="n">
         <v>0.2095</v>
@@ -5955,13 +5955,13 @@
         <v>20.98989898989895</v>
       </c>
       <c r="D191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>0.02918641045425666</v>
+        <v>0.02919462966099031</v>
       </c>
       <c r="G191" t="n">
         <v>0.2095</v>
@@ -5984,13 +5984,13 @@
         <v>21.09090909090905</v>
       </c>
       <c r="D192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>0.02914900794321644</v>
+        <v>0.02916602681137353</v>
       </c>
       <c r="G192" t="n">
         <v>0.2095</v>
@@ -6013,13 +6013,13 @@
         <v>21.19191919191915</v>
       </c>
       <c r="D193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>0.02917991482644801</v>
+        <v>0.02915269508448298</v>
       </c>
       <c r="G193" t="n">
         <v>0.2095</v>
@@ -6042,13 +6042,13 @@
         <v>21.29292929292925</v>
       </c>
       <c r="D194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>0.02918567105241813</v>
+        <v>0.02922561805446522</v>
       </c>
       <c r="G194" t="n">
         <v>0.2095</v>
@@ -6071,13 +6071,13 @@
         <v>21.39393939393935</v>
       </c>
       <c r="D195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>0.02913389183441236</v>
+        <v>0.02913184065382843</v>
       </c>
       <c r="G195" t="n">
         <v>0.2095</v>
@@ -6100,13 +6100,13 @@
         <v>21.49494949494945</v>
       </c>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0.02921987764225134</v>
+        <v>0.02914929003655873</v>
       </c>
       <c r="G196" t="n">
         <v>0.2095</v>
@@ -6129,13 +6129,13 @@
         <v>21.59595959595955</v>
       </c>
       <c r="D197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>0.02917158669654525</v>
+        <v>0.02918655718059781</v>
       </c>
       <c r="G197" t="n">
         <v>0.2095</v>
@@ -6158,13 +6158,13 @@
         <v>21.69696969696965</v>
       </c>
       <c r="D198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E198" t="n">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>0.02911256859086536</v>
+        <v>0.02912640563325007</v>
       </c>
       <c r="G198" t="n">
         <v>0.2095</v>
@@ -6187,13 +6187,13 @@
         <v>21.79797979797976</v>
       </c>
       <c r="D199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E199" t="n">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>0.0291953930595849</v>
+        <v>0.02918786488067226</v>
       </c>
       <c r="G199" t="n">
         <v>0.2095</v>
@@ -6216,13 +6216,13 @@
         <v>21.89898989898986</v>
       </c>
       <c r="D200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>0.02912937724021265</v>
+        <v>0.02914812405951983</v>
       </c>
       <c r="G200" t="n">
         <v>0.2095</v>
@@ -6245,13 +6245,13 @@
         <v>21.99999999999996</v>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>0.02915407683326279</v>
+        <v>0.02915813923567371</v>
       </c>
       <c r="G201" t="n">
         <v>0.2095</v>
@@ -6274,13 +6274,13 @@
         <v>22.99999999999996</v>
       </c>
       <c r="D202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>0.02915407683326279</v>
+        <v>0.02915813923567371</v>
       </c>
       <c r="G202" t="n">
         <v>0.2095</v>
@@ -6303,13 +6303,13 @@
         <v>23.10101010101006</v>
       </c>
       <c r="D203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>0.02916995893710692</v>
+        <v>0.02917136580343652</v>
       </c>
       <c r="G203" t="n">
         <v>0.2095</v>
@@ -6332,13 +6332,13 @@
         <v>23.20202020202016</v>
       </c>
       <c r="D204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>0.02916950483149414</v>
+        <v>0.02916896783493213</v>
       </c>
       <c r="G204" t="n">
         <v>0.2095</v>
@@ -6361,13 +6361,13 @@
         <v>23.30303030303026</v>
       </c>
       <c r="D205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>0.02918869506815995</v>
+        <v>0.02919030101773066</v>
       </c>
       <c r="G205" t="n">
         <v>0.2095</v>
@@ -6390,13 +6390,13 @@
         <v>23.40404040404036</v>
       </c>
       <c r="D206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>0.02917655136519006</v>
+        <v>0.02918343434916851</v>
       </c>
       <c r="G206" t="n">
         <v>0.2095</v>
@@ -6419,13 +6419,13 @@
         <v>23.50505050505046</v>
       </c>
       <c r="D207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>0.02915051729941648</v>
+        <v>0.02914779370409144</v>
       </c>
       <c r="G207" t="n">
         <v>0.2095</v>
@@ -6448,13 +6448,13 @@
         <v>23.60606060606056</v>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>0.02919382140392231</v>
+        <v>0.0291800739113723</v>
       </c>
       <c r="G208" t="n">
         <v>0.2095</v>
@@ -6477,13 +6477,13 @@
         <v>23.70707070707066</v>
       </c>
       <c r="D209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>0.02918017774549148</v>
+        <v>0.02918854883725652</v>
       </c>
       <c r="G209" t="n">
         <v>0.2095</v>
@@ -6506,13 +6506,13 @@
         <v>23.80808080808077</v>
       </c>
       <c r="D210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>0.0291345946243053</v>
+        <v>0.02913467396956734</v>
       </c>
       <c r="G210" t="n">
         <v>0.2095</v>
@@ -6535,13 +6535,13 @@
         <v>23.90909090909087</v>
       </c>
       <c r="D211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E211" t="n">
         <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>0.02922180348134698</v>
+        <v>0.02920216126793763</v>
       </c>
       <c r="G211" t="n">
         <v>0.2095</v>
@@ -6564,13 +6564,13 @@
         <v>24.01010101010097</v>
       </c>
       <c r="D212" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E212" t="n">
         <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>0.02916618603009595</v>
+        <v>0.02917251556480656</v>
       </c>
       <c r="G212" t="n">
         <v>0.2095</v>
@@ -6593,13 +6593,13 @@
         <v>24.11111111111107</v>
       </c>
       <c r="D213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E213" t="n">
         <v>0</v>
       </c>
       <c r="F213" t="n">
-        <v>0.02911707516545051</v>
+        <v>0.0291319129908599</v>
       </c>
       <c r="G213" t="n">
         <v>0.2095</v>
@@ -6622,13 +6622,13 @@
         <v>24.21212121212117</v>
       </c>
       <c r="D214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E214" t="n">
         <v>0</v>
       </c>
       <c r="F214" t="n">
-        <v>0.02919529567033597</v>
+        <v>0.02922931004370978</v>
       </c>
       <c r="G214" t="n">
         <v>0.2095</v>
@@ -6651,13 +6651,13 @@
         <v>24.31313131313127</v>
       </c>
       <c r="D215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E215" t="n">
         <v>0</v>
       </c>
       <c r="F215" t="n">
-        <v>0.02912706945947512</v>
+        <v>0.02913323717718112</v>
       </c>
       <c r="G215" t="n">
         <v>0.2095</v>
@@ -6680,13 +6680,13 @@
         <v>24.41414141414137</v>
       </c>
       <c r="D216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
       </c>
       <c r="F216" t="n">
-        <v>0.02917868825034305</v>
+        <v>0.02914866627386583</v>
       </c>
       <c r="G216" t="n">
         <v>0.2095</v>
@@ -6709,13 +6709,13 @@
         <v>24.51515151515147</v>
       </c>
       <c r="D217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>0.02916358748475114</v>
+        <v>0.0292081547916974</v>
       </c>
       <c r="G217" t="n">
         <v>0.2095</v>
@@ -6738,13 +6738,13 @@
         <v>24.61616161616157</v>
       </c>
       <c r="D218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E218" t="n">
         <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>0.02916224185825495</v>
+        <v>0.02909644747775066</v>
       </c>
       <c r="G218" t="n">
         <v>0.2095</v>
@@ -6767,13 +6767,13 @@
         <v>24.71717171717167</v>
       </c>
       <c r="D219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E219" t="n">
         <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>0.02919663098312125</v>
+        <v>0.02918679818372968</v>
       </c>
       <c r="G219" t="n">
         <v>0.2095</v>
@@ -6796,13 +6796,13 @@
         <v>24.81818181818177</v>
       </c>
       <c r="D220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E220" t="n">
         <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>0.0291363553184276</v>
+        <v>0.02914828799224567</v>
       </c>
       <c r="G220" t="n">
         <v>0.2095</v>
@@ -6825,13 +6825,13 @@
         <v>24.91919191919188</v>
       </c>
       <c r="D221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E221" t="n">
         <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>0.02920001255130113</v>
+        <v>0.02916248128834567</v>
       </c>
       <c r="G221" t="n">
         <v>0.2095</v>
@@ -6854,13 +6854,13 @@
         <v>25.02020202020198</v>
       </c>
       <c r="D222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E222" t="n">
         <v>0</v>
       </c>
       <c r="F222" t="n">
-        <v>0.02920006247087261</v>
+        <v>0.02918134920155742</v>
       </c>
       <c r="G222" t="n">
         <v>0.2095</v>
@@ -6883,13 +6883,13 @@
         <v>25.12121212121208</v>
       </c>
       <c r="D223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E223" t="n">
         <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>0.02909835761728981</v>
+        <v>0.02914124714469928</v>
       </c>
       <c r="G223" t="n">
         <v>0.2095</v>
@@ -6912,13 +6912,13 @@
         <v>25.22222222222218</v>
       </c>
       <c r="D224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E224" t="n">
         <v>0</v>
       </c>
       <c r="F224" t="n">
-        <v>0.0291894302621057</v>
+        <v>0.02920042734396092</v>
       </c>
       <c r="G224" t="n">
         <v>0.2095</v>
@@ -6941,13 +6941,13 @@
         <v>25.32323232323228</v>
       </c>
       <c r="D225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E225" t="n">
         <v>0</v>
       </c>
       <c r="F225" t="n">
-        <v>0.02914873287013928</v>
+        <v>0.02915448708129321</v>
       </c>
       <c r="G225" t="n">
         <v>0.2095</v>
@@ -6970,13 +6970,13 @@
         <v>25.42424242424238</v>
       </c>
       <c r="D226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E226" t="n">
         <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>0.0291601852406742</v>
+        <v>0.02916491780259703</v>
       </c>
       <c r="G226" t="n">
         <v>0.2095</v>
@@ -6999,13 +6999,13 @@
         <v>25.52525252525248</v>
       </c>
       <c r="D227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E227" t="n">
         <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>0.02918016859311877</v>
+        <v>0.02922097454809373</v>
       </c>
       <c r="G227" t="n">
         <v>0.2095</v>
@@ -7028,13 +7028,13 @@
         <v>25.62626262626258</v>
       </c>
       <c r="D228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E228" t="n">
         <v>0</v>
       </c>
       <c r="F228" t="n">
-        <v>0.02914341785328277</v>
+        <v>0.02911397997426158</v>
       </c>
       <c r="G228" t="n">
         <v>0.2095</v>
@@ -7057,13 +7057,13 @@
         <v>25.72727272727268</v>
       </c>
       <c r="D229" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E229" t="n">
         <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>0.02919875423556655</v>
+        <v>0.02918493175307624</v>
       </c>
       <c r="G229" t="n">
         <v>0.2095</v>
@@ -7086,13 +7086,13 @@
         <v>25.82828282828278</v>
       </c>
       <c r="D230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E230" t="n">
         <v>0</v>
       </c>
       <c r="F230" t="n">
-        <v>0.02915404549935013</v>
+        <v>0.02920403230330732</v>
       </c>
       <c r="G230" t="n">
         <v>0.2095</v>
@@ -7115,13 +7115,13 @@
         <v>25.92929292929288</v>
       </c>
       <c r="D231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E231" t="n">
         <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>0.02916877443424735</v>
+        <v>0.02908459062413979</v>
       </c>
       <c r="G231" t="n">
         <v>0.2095</v>
@@ -7144,13 +7144,13 @@
         <v>26.03030303030299</v>
       </c>
       <c r="D232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E232" t="n">
         <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>0.02922084117530908</v>
+        <v>0.02919769934105143</v>
       </c>
       <c r="G232" t="n">
         <v>0.2095</v>
@@ -7173,13 +7173,13 @@
         <v>26.13131313131309</v>
       </c>
       <c r="D233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E233" t="n">
         <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>0.02911406686083273</v>
+        <v>0.02913644589585904</v>
       </c>
       <c r="G233" t="n">
         <v>0.2095</v>
@@ -7202,13 +7202,13 @@
         <v>26.23232323232319</v>
       </c>
       <c r="D234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E234" t="n">
         <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>0.02916755674224996</v>
+        <v>0.02916070954581841</v>
       </c>
       <c r="G234" t="n">
         <v>0.2095</v>
@@ -7231,13 +7231,13 @@
         <v>26.33333333333329</v>
       </c>
       <c r="D235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E235" t="n">
         <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>0.02917502995272393</v>
+        <v>0.02917510030896179</v>
       </c>
       <c r="G235" t="n">
         <v>0.2095</v>
@@ -7260,13 +7260,13 @@
         <v>26.43434343434339</v>
       </c>
       <c r="D236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E236" t="n">
         <v>0</v>
       </c>
       <c r="F236" t="n">
-        <v>0.0291372323572113</v>
+        <v>0.02914617527660097</v>
       </c>
       <c r="G236" t="n">
         <v>0.2095</v>
@@ -7289,13 +7289,13 @@
         <v>26.53535353535349</v>
       </c>
       <c r="D237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E237" t="n">
         <v>0</v>
       </c>
       <c r="F237" t="n">
-        <v>0.02918874401016149</v>
+        <v>0.02919381977515265</v>
       </c>
       <c r="G237" t="n">
         <v>0.2095</v>
@@ -7318,13 +7318,13 @@
         <v>26.63636363636359</v>
       </c>
       <c r="D238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E238" t="n">
         <v>0</v>
       </c>
       <c r="F238" t="n">
-        <v>0.02914096173331251</v>
+        <v>0.0291454054523103</v>
       </c>
       <c r="G238" t="n">
         <v>0.2095</v>
@@ -7347,13 +7347,13 @@
         <v>26.73737373737369</v>
       </c>
       <c r="D239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E239" t="n">
         <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>0.02918869561287705</v>
+        <v>0.02918655064609318</v>
       </c>
       <c r="G239" t="n">
         <v>0.2095</v>
@@ -7376,13 +7376,13 @@
         <v>26.83838383838379</v>
       </c>
       <c r="D240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E240" t="n">
         <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>0.02917604984949133</v>
+        <v>0.02919864461068498</v>
       </c>
       <c r="G240" t="n">
         <v>0.2095</v>
@@ -7405,13 +7405,13 @@
         <v>26.9393939393939</v>
       </c>
       <c r="D241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E241" t="n">
         <v>0</v>
       </c>
       <c r="F241" t="n">
-        <v>0.02914046500560479</v>
+        <v>0.02911429708037552</v>
       </c>
       <c r="G241" t="n">
         <v>0.2095</v>
@@ -7434,13 +7434,13 @@
         <v>27.040404040404</v>
       </c>
       <c r="D242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E242" t="n">
         <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>0.0292235726467644</v>
+        <v>0.02921921457857756</v>
       </c>
       <c r="G242" t="n">
         <v>0.2095</v>
@@ -7463,13 +7463,13 @@
         <v>27.1414141414141</v>
       </c>
       <c r="D243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E243" t="n">
         <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>0.02914810406649536</v>
+        <v>0.02918282747833126</v>
       </c>
       <c r="G243" t="n">
         <v>0.2095</v>
@@ -7492,13 +7492,13 @@
         <v>27.2424242424242</v>
       </c>
       <c r="D244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E244" t="n">
         <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>0.02914206238782563</v>
+        <v>0.02909241976095697</v>
       </c>
       <c r="G244" t="n">
         <v>0.2095</v>
@@ -7521,13 +7521,13 @@
         <v>27.3434343434343</v>
       </c>
       <c r="D245" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E245" t="n">
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>0.02923238461976402</v>
+        <v>0.02921683384146934</v>
       </c>
       <c r="G245" t="n">
         <v>0.2095</v>
@@ -7550,13 +7550,13 @@
         <v>27.4444444444444</v>
       </c>
       <c r="D246" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E246" t="n">
         <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>0.02909642335156142</v>
+        <v>0.029119452835571</v>
       </c>
       <c r="G246" t="n">
         <v>0.2095</v>
@@ -7579,13 +7579,13 @@
         <v>27.5454545454545</v>
       </c>
       <c r="D247" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E247" t="n">
         <v>0</v>
       </c>
       <c r="F247" t="n">
-        <v>0.02917112442960171</v>
+        <v>0.02915886739718954</v>
       </c>
       <c r="G247" t="n">
         <v>0.2095</v>
@@ -7608,13 +7608,13 @@
         <v>27.6464646464646</v>
       </c>
       <c r="D248" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E248" t="n">
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>0.02917228496615614</v>
+        <v>0.02917093636756315</v>
       </c>
       <c r="G248" t="n">
         <v>0.2095</v>
@@ -7637,13 +7637,13 @@
         <v>27.7474747474747</v>
       </c>
       <c r="D249" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E249" t="n">
         <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>0.02912904005220966</v>
+        <v>0.02914467914144549</v>
       </c>
       <c r="G249" t="n">
         <v>0.2095</v>
@@ -7666,13 +7666,13 @@
         <v>27.84848484848481</v>
       </c>
       <c r="D250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E250" t="n">
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>0.02918609191862729</v>
+        <v>0.02918745718647649</v>
       </c>
       <c r="G250" t="n">
         <v>0.2095</v>
@@ -7695,13 +7695,13 @@
         <v>27.94949494949491</v>
       </c>
       <c r="D251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E251" t="n">
         <v>0</v>
       </c>
       <c r="F251" t="n">
-        <v>0.02913615205492451</v>
+        <v>0.02914238538549742</v>
       </c>
       <c r="G251" t="n">
         <v>0.2095</v>
@@ -7724,13 +7724,13 @@
         <v>28.05050505050501</v>
       </c>
       <c r="D252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E252" t="n">
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>0.02918749498099872</v>
+        <v>0.02919258613526592</v>
       </c>
       <c r="G252" t="n">
         <v>0.2095</v>
@@ -7753,13 +7753,13 @@
         <v>28.15151515151511</v>
       </c>
       <c r="D253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E253" t="n">
         <v>0</v>
       </c>
       <c r="F253" t="n">
-        <v>0.02916308842873404</v>
+        <v>0.02917649755803797</v>
       </c>
       <c r="G253" t="n">
         <v>0.2095</v>
@@ -7782,13 +7782,13 @@
         <v>28.25252525252521</v>
       </c>
       <c r="D254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E254" t="n">
         <v>0</v>
       </c>
       <c r="F254" t="n">
-        <v>0.02916330315168214</v>
+        <v>0.02913729327528744</v>
       </c>
       <c r="G254" t="n">
         <v>0.2095</v>
@@ -7811,13 +7811,13 @@
         <v>28.35353535353531</v>
       </c>
       <c r="D255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E255" t="n">
         <v>0</v>
       </c>
       <c r="F255" t="n">
-        <v>0.02921054059225838</v>
+        <v>0.02923067864624492</v>
       </c>
       <c r="G255" t="n">
         <v>0.2095</v>
@@ -7840,13 +7840,13 @@
         <v>28.45454545454541</v>
       </c>
       <c r="D256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E256" t="n">
         <v>0</v>
       </c>
       <c r="F256" t="n">
-        <v>0.02913091535161005</v>
+        <v>0.02915115069645883</v>
       </c>
       <c r="G256" t="n">
         <v>0.2095</v>
@@ -7869,13 +7869,13 @@
         <v>28.55555555555551</v>
       </c>
       <c r="D257" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E257" t="n">
         <v>0</v>
       </c>
       <c r="F257" t="n">
-        <v>0.02918727415345202</v>
+        <v>0.02912330392625321</v>
       </c>
       <c r="G257" t="n">
         <v>0.2095</v>
@@ -7898,13 +7898,13 @@
         <v>28.65656565656561</v>
       </c>
       <c r="D258" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E258" t="n">
         <v>0</v>
       </c>
       <c r="F258" t="n">
-        <v>0.02922217317281399</v>
+        <v>0.02919117198457874</v>
       </c>
       <c r="G258" t="n">
         <v>0.2095</v>
@@ -7927,13 +7927,13 @@
         <v>28.75757575757572</v>
       </c>
       <c r="D259" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E259" t="n">
         <v>0</v>
       </c>
       <c r="F259" t="n">
-        <v>0.02908096881166574</v>
+        <v>0.02912344550139351</v>
       </c>
       <c r="G259" t="n">
         <v>0.2095</v>
@@ -7956,13 +7956,13 @@
         <v>28.85858585858582</v>
       </c>
       <c r="D260" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E260" t="n">
         <v>0</v>
       </c>
       <c r="F260" t="n">
-        <v>0.02919849580226917</v>
+        <v>0.02918193967979324</v>
       </c>
       <c r="G260" t="n">
         <v>0.2095</v>
@@ -7985,13 +7985,13 @@
         <v>28.95959595959592</v>
       </c>
       <c r="D261" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E261" t="n">
         <v>0</v>
       </c>
       <c r="F261" t="n">
-        <v>0.02916617567018928</v>
+        <v>0.02915503102854668</v>
       </c>
       <c r="G261" t="n">
         <v>0.2095</v>
@@ -8014,13 +8014,13 @@
         <v>29.06060606060602</v>
       </c>
       <c r="D262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E262" t="n">
         <v>0</v>
       </c>
       <c r="F262" t="n">
-        <v>0.02911807641920844</v>
+        <v>0.0291741983258382</v>
       </c>
       <c r="G262" t="n">
         <v>0.2095</v>
@@ -8043,13 +8043,13 @@
         <v>29.16161616161612</v>
       </c>
       <c r="D263" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E263" t="n">
         <v>0</v>
       </c>
       <c r="F263" t="n">
-        <v>0.02918724986113345</v>
+        <v>0.02918917388935463</v>
       </c>
       <c r="G263" t="n">
         <v>0.2095</v>
@@ -8072,13 +8072,13 @@
         <v>29.26262626262622</v>
       </c>
       <c r="D264" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E264" t="n">
         <v>0</v>
       </c>
       <c r="F264" t="n">
-        <v>0.02912707417437358</v>
+        <v>0.02913536928120935</v>
       </c>
       <c r="G264" t="n">
         <v>0.2095</v>
@@ -8101,13 +8101,13 @@
         <v>29.36363636363632</v>
       </c>
       <c r="D265" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E265" t="n">
         <v>0</v>
       </c>
       <c r="F265" t="n">
-        <v>0.02918400837559462</v>
+        <v>0.02921545957658241</v>
       </c>
       <c r="G265" t="n">
         <v>0.2095</v>
@@ -8130,13 +8130,13 @@
         <v>29.46464646464642</v>
       </c>
       <c r="D266" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E266" t="n">
         <v>0</v>
       </c>
       <c r="F266" t="n">
-        <v>0.02915509958133683</v>
+        <v>0.02918582912214237</v>
       </c>
       <c r="G266" t="n">
         <v>0.2095</v>
@@ -8159,13 +8159,13 @@
         <v>29.56565656565652</v>
       </c>
       <c r="D267" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E267" t="n">
         <v>0</v>
       </c>
       <c r="F267" t="n">
-        <v>0.02917468873802801</v>
+        <v>0.02909993054893642</v>
       </c>
       <c r="G267" t="n">
         <v>0.2095</v>
@@ -8188,13 +8188,13 @@
         <v>29.66666666666663</v>
       </c>
       <c r="D268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E268" t="n">
         <v>0</v>
       </c>
       <c r="F268" t="n">
-        <v>0.02919224932434681</v>
+        <v>0.02919267474115264</v>
       </c>
       <c r="G268" t="n">
         <v>0.2095</v>
@@ -8217,13 +8217,13 @@
         <v>29.76767676767673</v>
       </c>
       <c r="D269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E269" t="n">
         <v>0</v>
       </c>
       <c r="F269" t="n">
-        <v>0.02913223259782753</v>
+        <v>0.02913763429811472</v>
       </c>
       <c r="G269" t="n">
         <v>0.2095</v>
@@ -8246,13 +8246,13 @@
         <v>29.86868686868683</v>
       </c>
       <c r="D270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E270" t="n">
         <v>0</v>
       </c>
       <c r="F270" t="n">
-        <v>0.02921473836690556</v>
+        <v>0.02916933241108743</v>
       </c>
       <c r="G270" t="n">
         <v>0.2095</v>
@@ -8275,13 +8275,13 @@
         <v>29.96969696969693</v>
       </c>
       <c r="D271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E271" t="n">
         <v>0</v>
       </c>
       <c r="F271" t="n">
-        <v>0.02919097862963112</v>
+        <v>0.02917205173500921</v>
       </c>
       <c r="G271" t="n">
         <v>0.2095</v>
@@ -8304,13 +8304,13 @@
         <v>30.07070707070703</v>
       </c>
       <c r="D272" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0.02909341076668931</v>
+        <v>0.02915373099615052</v>
       </c>
       <c r="G272" t="n">
         <v>0.2095</v>
@@ -8333,13 +8333,13 @@
         <v>30.17171717171713</v>
       </c>
       <c r="D273" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0.02919061554446118</v>
+        <v>0.02919866666891546</v>
       </c>
       <c r="G273" t="n">
         <v>0.2095</v>
@@ -8362,13 +8362,13 @@
         <v>30.27272727272723</v>
       </c>
       <c r="D274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.02913816583593284</v>
+        <v>0.0291448159999473</v>
       </c>
       <c r="G274" t="n">
         <v>0.2095</v>
@@ -8391,13 +8391,13 @@
         <v>30.37373737373733</v>
       </c>
       <c r="D275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.02916798650671103</v>
+        <v>0.02918588583877702</v>
       </c>
       <c r="G275" t="n">
         <v>0.2095</v>
@@ -8420,13 +8420,13 @@
         <v>30.47474747474743</v>
       </c>
       <c r="D276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.02917136649171122</v>
+        <v>0.029215728675896</v>
       </c>
       <c r="G276" t="n">
         <v>0.2095</v>
@@ -8449,13 +8449,13 @@
         <v>30.57575757575753</v>
       </c>
       <c r="D277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.02915545138028492</v>
+        <v>0.02910175043141518</v>
       </c>
       <c r="G277" t="n">
         <v>0.2095</v>
@@ -8478,13 +8478,13 @@
         <v>30.67676767676763</v>
       </c>
       <c r="D278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.02919739855945198</v>
+        <v>0.02917631209207757</v>
       </c>
       <c r="G278" t="n">
         <v>0.2095</v>
@@ -8507,13 +8507,13 @@
         <v>30.77777777777774</v>
       </c>
       <c r="D279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0.02914524289707226</v>
+        <v>0.0291637135776825</v>
       </c>
       <c r="G279" t="n">
         <v>0.2095</v>
@@ -8536,13 +8536,13 @@
         <v>30.87878787878784</v>
       </c>
       <c r="D280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E280" t="n">
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.02918823888225247</v>
+        <v>0.0291476626558888</v>
       </c>
       <c r="G280" t="n">
         <v>0.2095</v>
@@ -8565,13 +8565,13 @@
         <v>30.97979797979794</v>
       </c>
       <c r="D281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0.02921647282813545</v>
+        <v>0.02918462590578904</v>
       </c>
       <c r="G281" t="n">
         <v>0.2095</v>
@@ -8594,13 +8594,13 @@
         <v>31.08080808080804</v>
       </c>
       <c r="D282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E282" t="n">
         <v>0</v>
       </c>
       <c r="F282" t="n">
-        <v>0.02910134291853948</v>
+        <v>0.02914101235339456</v>
       </c>
       <c r="G282" t="n">
         <v>0.2095</v>
@@ -8623,13 +8623,13 @@
         <v>31.18181818181814</v>
       </c>
       <c r="D283" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E283" t="n">
         <v>0</v>
       </c>
       <c r="F283" t="n">
-        <v>0.02917468045069893</v>
+        <v>0.02919468817768069</v>
       </c>
       <c r="G283" t="n">
         <v>0.2095</v>
@@ -8652,13 +8652,13 @@
         <v>31.28282828282824</v>
       </c>
       <c r="D284" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E284" t="n">
         <v>0</v>
       </c>
       <c r="F284" t="n">
-        <v>0.02916413053302522</v>
+        <v>0.02916546610803605</v>
       </c>
       <c r="G284" t="n">
         <v>0.2095</v>
@@ -8681,13 +8681,13 @@
         <v>31.38383838383834</v>
       </c>
       <c r="D285" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E285" t="n">
         <v>0</v>
       </c>
       <c r="F285" t="n">
-        <v>0.02914756113956213</v>
+        <v>0.02915417222209647</v>
       </c>
       <c r="G285" t="n">
         <v>0.2095</v>
@@ -8710,13 +8710,13 @@
         <v>31.48484848484844</v>
       </c>
       <c r="D286" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E286" t="n">
         <v>0</v>
       </c>
       <c r="F286" t="n">
-        <v>0.02918397028330463</v>
+        <v>0.02922694682510097</v>
       </c>
       <c r="G286" t="n">
         <v>0.2095</v>
@@ -8739,13 +8739,13 @@
         <v>31.58585858585855</v>
       </c>
       <c r="D287" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E287" t="n">
         <v>0</v>
       </c>
       <c r="F287" t="n">
-        <v>0.0291420242291085</v>
+        <v>0.02913175449657731</v>
       </c>
       <c r="G287" t="n">
         <v>0.2095</v>
@@ -8768,13 +8768,13 @@
         <v>31.68686868686864</v>
       </c>
       <c r="D288" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E288" t="n">
         <v>0</v>
       </c>
       <c r="F288" t="n">
-        <v>0.02919464376867533</v>
+        <v>0.02914735274442671</v>
       </c>
       <c r="G288" t="n">
         <v>0.2095</v>
@@ -8797,13 +8797,13 @@
         <v>31.78787878787875</v>
       </c>
       <c r="D289" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E289" t="n">
         <v>0</v>
       </c>
       <c r="F289" t="n">
-        <v>0.02916551256831027</v>
+        <v>0.02918633846065801</v>
       </c>
       <c r="G289" t="n">
         <v>0.2095</v>
@@ -8826,13 +8826,13 @@
         <v>31.88888888888885</v>
       </c>
       <c r="D290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E290" t="n">
         <v>0</v>
       </c>
       <c r="F290" t="n">
-        <v>0.02915460543782547</v>
+        <v>0.02912671363194239</v>
       </c>
       <c r="G290" t="n">
         <v>0.2095</v>
@@ -8855,13 +8855,13 @@
         <v>31.98989898989895</v>
       </c>
       <c r="D291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E291" t="n">
         <v>0</v>
       </c>
       <c r="F291" t="n">
-        <v>0.02922845961588006</v>
+        <v>0.02918705483827997</v>
       </c>
       <c r="G291" t="n">
         <v>0.2095</v>
@@ -8884,13 +8884,13 @@
         <v>32.09090909090905</v>
       </c>
       <c r="D292" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E292" t="n">
         <v>0</v>
       </c>
       <c r="F292" t="n">
-        <v>0.02913257254459496</v>
+        <v>0.02914839846385785</v>
       </c>
       <c r="G292" t="n">
         <v>0.2095</v>
@@ -8913,13 +8913,13 @@
         <v>32.19191919191915</v>
       </c>
       <c r="D293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E293" t="n">
         <v>0</v>
       </c>
       <c r="F293" t="n">
-        <v>0.02914443225173647</v>
+        <v>0.02918002961239456</v>
       </c>
       <c r="G293" t="n">
         <v>0.2095</v>
@@ -8942,13 +8942,13 @@
         <v>32.29292929292925</v>
       </c>
       <c r="D294" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E294" t="n">
         <v>0</v>
       </c>
       <c r="F294" t="n">
-        <v>0.02918648421378546</v>
+        <v>0.02918559368722073</v>
       </c>
       <c r="G294" t="n">
         <v>0.2095</v>
@@ -8971,13 +8971,13 @@
         <v>32.39393939393936</v>
       </c>
       <c r="D295" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E295" t="n">
         <v>0</v>
       </c>
       <c r="F295" t="n">
-        <v>0.02912662135251541</v>
+        <v>0.02913352966486945</v>
       </c>
       <c r="G295" t="n">
         <v>0.2095</v>
@@ -9000,13 +9000,13 @@
         <v>32.49494949494945</v>
       </c>
       <c r="D296" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E296" t="n">
         <v>0</v>
       </c>
       <c r="F296" t="n">
-        <v>0.02918614443675914</v>
+        <v>0.02921948250184843</v>
       </c>
       <c r="G296" t="n">
         <v>0.2095</v>
@@ -9029,13 +9029,13 @@
         <v>32.59595959595956</v>
       </c>
       <c r="D297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E297" t="n">
         <v>0</v>
       </c>
       <c r="F297" t="n">
-        <v>0.02914899669170457</v>
+        <v>0.02916999748604408</v>
       </c>
       <c r="G297" t="n">
         <v>0.2095</v>
@@ -9058,13 +9058,13 @@
         <v>32.69696969696965</v>
       </c>
       <c r="D298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E298" t="n">
         <v>0</v>
       </c>
       <c r="F298" t="n">
-        <v>0.0291802693096489</v>
+        <v>0.02911493341673261</v>
       </c>
       <c r="G298" t="n">
         <v>0.2095</v>
@@ -9087,13 +9087,13 @@
         <v>32.79797979797976</v>
       </c>
       <c r="D299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E299" t="n">
         <v>0</v>
       </c>
       <c r="F299" t="n">
-        <v>0.02918529271093486</v>
+        <v>0.02919581721642732</v>
       </c>
       <c r="G299" t="n">
         <v>0.2095</v>
@@ -9113,16 +9113,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>32.89898989898986</v>
+        <v>32.89898989898985</v>
       </c>
       <c r="D300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E300" t="n">
         <v>0</v>
       </c>
       <c r="F300" t="n">
-        <v>0.02913430757733993</v>
+        <v>0.02912863643598632</v>
       </c>
       <c r="G300" t="n">
         <v>0.2095</v>
@@ -9142,16 +9142,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>32.99999999999996</v>
+        <v>32.99999999999995</v>
       </c>
       <c r="D301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E301" t="n">
         <v>0</v>
       </c>
       <c r="F301" t="n">
-        <v>0.02916195705272219</v>
+        <v>0.02915423609274065</v>
       </c>
       <c r="G301" t="n">
         <v>0.2095</v>
